--- a/foy-portfoy-takip-excel.xlsx
+++ b/foy-portfoy-takip-excel.xlsx
@@ -146,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -172,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -205,9 +208,9 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Krem renkli hücreleri siz doldurun; beyaz hücreleri Excel hesaplar. Güncel fiyatlar elle girilir — şablon dışarıdan veri çekmez.</t>
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Krem hücreleri siz doldurun, beyaz hücreleri Excel hesaplar. Güncel fiyatlar elle girilir — şablon dışarıdan veri çekmez.</t>
         </is>
       </c>
     </row>
@@ -1332,9 +1335,9 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bu sayfadaki her sayı Portföy sayfasından otomatik gelir. Buraya elle bir şey yazmanız gerekmez.</t>
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bu sayfadaki her sayı Portföy sayfasından gelir; buraya elle bir şey yazmanız gerekmez.</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1685,7 @@
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FÖY; fiyatları kendisi günceller, her alım-satımı ve temettüyü kalıcı olarak kaydeder, ortalama maliyeti sizin girdiğiniz gerçek alış fiyatından hesaplar. Hesap açmanız gerekmez, veriler cihazınızda kalır.</t>
+          <t xml:space="preserve">FÖY; fiyatları kendisi günceller, girdiğiniz her alım-satımı ve temettüyü kalıcı olarak saklar, ortalama maliyeti sizin girdiğiniz gerçek alış fiyatından hesaplar. Hesap açmanız gerekmez, veriler cihazınızda kalır.</t>
         </is>
       </c>
     </row>
